--- a/artfynd/A 45131-2023 artfynd.xlsx
+++ b/artfynd/A 45131-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126022586</v>
       </c>
       <c r="B2" t="n">
-        <v>97437</v>
+        <v>97439</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 45131-2023 artfynd.xlsx
+++ b/artfynd/A 45131-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126022586</v>
       </c>
       <c r="B2" t="n">
-        <v>97439</v>
+        <v>97443</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 45131-2023 artfynd.xlsx
+++ b/artfynd/A 45131-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126022586</v>
       </c>
       <c r="B2" t="n">
-        <v>97443</v>
+        <v>97444</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 45131-2023 artfynd.xlsx
+++ b/artfynd/A 45131-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126022586</v>
       </c>
       <c r="B2" t="n">
-        <v>97444</v>
+        <v>97446</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 45131-2023 artfynd.xlsx
+++ b/artfynd/A 45131-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126022586</v>
       </c>
       <c r="B2" t="n">
-        <v>97446</v>
+        <v>97448</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 45131-2023 artfynd.xlsx
+++ b/artfynd/A 45131-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126022586</v>
       </c>
       <c r="B2" t="n">
-        <v>97448</v>
+        <v>97450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 45131-2023 artfynd.xlsx
+++ b/artfynd/A 45131-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126022586</v>
       </c>
       <c r="B2" t="n">
-        <v>97450</v>
+        <v>97454</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 45131-2023 artfynd.xlsx
+++ b/artfynd/A 45131-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126022586</v>
       </c>
       <c r="B2" t="n">
-        <v>97454</v>
+        <v>97457</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 45131-2023 artfynd.xlsx
+++ b/artfynd/A 45131-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126022586</v>
       </c>
       <c r="B2" t="n">
-        <v>97457</v>
+        <v>97466</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
